--- a/docs/eu/StructureDefinition-ImImagingStudy.xlsx
+++ b/docs/eu/StructureDefinition-ImImagingStudy.xlsx
@@ -955,7 +955,7 @@
     <t>wado</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImWadoEndpoint|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImWadoEndpoint|0.0.2)
 </t>
   </si>
   <si>
@@ -965,7 +965,7 @@
     <t>iid</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImImageIidViewerEndpoint|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImImageIidViewerEndpoint|0.0.2)
 </t>
   </si>
   <si>
